--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
